--- a/Plot/exposures_meta_analysis_uterine_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_dietary.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -522,737 +522,743 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>eggs</t>
+          <t>vitamin_d</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.27</v>
+        <v>0.41</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.36</v>
+        <v>0.2</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F2" s="4" t="inlineStr"/>
-      <c r="G2" s="4" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
       <c r="H2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="6" t="inlineStr"/>
+      <c r="I2" s="6" t="n"/>
       <c r="J2" s="3" t="n">
-        <v>541</v>
+        <v>714</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>161</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>vitamin_d</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.41</v>
+        <v>0.49</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F3" s="4" t="inlineStr"/>
-      <c r="G3" s="4" t="inlineStr"/>
+        <v>0.73</v>
+      </c>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
       <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="6" t="inlineStr"/>
+      <c r="I3" s="6" t="n"/>
       <c r="J3" s="3" t="n">
-        <v>714</v>
+        <v>74680</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>85</v>
+        <v>412</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>legumes</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr"/>
-      <c r="G4" s="4" t="inlineStr"/>
+        <v>0.85</v>
+      </c>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="n"/>
       <c r="J4" s="3" t="n">
-        <v>1082</v>
+        <v>843</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>541</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>legumes</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr"/>
-      <c r="G5" s="4" t="inlineStr"/>
+        <v>0.71</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>26.86</v>
+      </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr"/>
+        <v>62.8</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.2282168407301836</v>
+      </c>
       <c r="J5" s="3" t="n">
-        <v>843</v>
+        <v>3315</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>332</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>mineral_supplements</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr"/>
-      <c r="G6" s="4" t="inlineStr"/>
+        <v>0.91</v>
+      </c>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
       <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="n"/>
       <c r="J6" s="3" t="n">
-        <v>74680</v>
+        <v>3596</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>412</v>
+        <v>709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>vitamin_c</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>26.86</v>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
       <c r="H7" s="5" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>0.2282168407301835</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7" s="6" t="n"/>
       <c r="J7" s="3" t="n">
-        <v>3315</v>
+        <v>871</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>vitamin_c</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="F8" s="4" t="inlineStr"/>
-      <c r="G8" s="4" t="inlineStr"/>
+        <v>0.78</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>5.64</v>
+      </c>
       <c r="H8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr"/>
+        <v>24.9</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>0.1753492059479154</v>
+      </c>
       <c r="J8" s="3" t="n">
-        <v>871</v>
+        <v>3315</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>232</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mineral_supplements</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr"/>
-      <c r="G9" s="4" t="inlineStr"/>
+        <v>1.08</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>509.19</v>
+      </c>
       <c r="H9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr"/>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.484788327891376</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>3596</v>
+        <v>90098</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>709</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>5.64</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
       <c r="H10" s="5" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>0.1753492059479153</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I10" s="6" t="n"/>
       <c r="J10" s="3" t="n">
-        <v>3315</v>
+        <v>812</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1227</v>
+        <v>417</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>garlic</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>509.19</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
       <c r="H11" s="5" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="I11" s="6" t="n">
-        <v>0.4847883278913757</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I11" s="6" t="n"/>
       <c r="J11" s="3" t="n">
-        <v>90098</v>
+        <v>1362</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>3100</v>
+        <v>454</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>antioxidants</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.42</v>
+        <v>0.55</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr"/>
-      <c r="G12" s="4" t="inlineStr"/>
+        <v>0.84</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1.09</v>
+      </c>
       <c r="H12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="6" t="inlineStr"/>
+        <v>0.6</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.084037740305833</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>812</v>
+        <v>6240</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>417</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>garlic</t>
+          <t>quercetin</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F13" s="4" t="inlineStr"/>
-      <c r="G13" s="4" t="inlineStr"/>
+        <v>1.01</v>
+      </c>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
       <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="6" t="inlineStr"/>
+      <c r="I13" s="6" t="n"/>
       <c r="J13" s="3" t="n">
-        <v>1362</v>
+        <v>822</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>454</v>
+        <v>424</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>quercetin</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.68</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr"/>
+        <v>1.24</v>
+      </c>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
       <c r="H14" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="6" t="inlineStr"/>
+        <v>86.2</v>
+      </c>
+      <c r="I14" s="6" t="n"/>
       <c r="J14" s="3" t="n">
-        <v>822</v>
+        <v>30376</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>424</v>
+        <v>2937</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>green_tea</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.55</v>
+        <v>0.51</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.43</v>
+        <v>0.03</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.09</v>
+        <v>16.43</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.6</v>
+        <v>46.3</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.084037740305833</v>
+        <v>0.3550326464827145</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>6240</v>
+        <v>3331</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>1445</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>green_tea</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="B16" s="3" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>16.43</v>
+        <v>127.74</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>46.3</v>
+        <v>84.2</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.3550326464827144</v>
+        <v>0.0290298668942214</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>3331</v>
+        <v>95991</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1564</v>
+        <v>933</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>soy</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.73</v>
+        <v>0.76</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>0.48</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>127.74</v>
+        <v>5.72</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>84.2</v>
+        <v>78.7</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.02902986689422141</v>
+        <v>0.8535116576994071</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>95991</v>
+        <v>4413</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>933</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>olive</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.48</v>
+        <v>0.57</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>5.72</v>
-      </c>
+        <v>1.25</v>
+      </c>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
       <c r="H18" s="5" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>0.8535116576994072</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I18" s="6" t="n"/>
       <c r="J18" s="3" t="n">
-        <v>4413</v>
+        <v>443</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>2105</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>olive</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
+        <v>1.19</v>
+      </c>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
       <c r="H19" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr"/>
+        <v>59.9</v>
+      </c>
+      <c r="I19" s="6" t="n"/>
       <c r="J19" s="3" t="n">
-        <v>443</v>
+        <v>2233</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>145</v>
+        <v>686</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>vitamin_b12</t>
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.54</v>
+        <v>0.74</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
+        <v>0.93</v>
+      </c>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
       <c r="H20" s="5" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="6" t="n"/>
       <c r="J20" s="3" t="n">
-        <v>2233</v>
+        <v>12437</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>686</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vitamin_b12</t>
+          <t>omega-3_fatty_acids</t>
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.74</v>
+        <v>0.64</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F21" s="4" t="inlineStr"/>
-      <c r="G21" s="4" t="inlineStr"/>
+        <v>1.15</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>2.43</v>
+      </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr"/>
+        <v>81.59999999999999</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.6898302519232826</v>
+      </c>
       <c r="J21" s="3" t="n">
-        <v>12437</v>
+        <v>457863</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>386</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>omega-3_fatty_acids</t>
+          <t>fish_oil</t>
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.64</v>
+        <v>0.48</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.15</v>
+        <v>1.61</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.43</v>
+        <v>1689.46</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>81.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.6898302519232826</v>
+        <v>0.4263170110816271</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>457863</v>
+        <v>110943</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>4240</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fish_oil</t>
+          <t>caffeine</t>
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1689.46</v>
+        <v>2.07</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>89.5</v>
+        <v>60.8</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.4263170110816271</v>
+        <v>0.8631142054417384</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>110943</v>
+        <v>150854</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>2072</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="24">
@@ -1265,25 +1271,25 @@
         <v>15</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.57</v>
+        <v>0.66</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>80.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.4229946346679966</v>
+        <v>0.7559650135603327</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>411289</v>
@@ -1295,234 +1301,197 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>caffeine</t>
+          <t>phosphorus</t>
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>2.07</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
       <c r="H25" s="5" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>0.8631142054417384</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I25" s="6" t="n"/>
       <c r="J25" s="3" t="n">
-        <v>150854</v>
+        <v>12437</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1222</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>phosphorus</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
+        <v>1.66</v>
+      </c>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
       <c r="H26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="6" t="inlineStr"/>
+      <c r="I26" s="6" t="n"/>
       <c r="J26" s="3" t="n">
-        <v>12437</v>
+        <v>1362</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>386</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.95</v>
+        <v>1.1</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr"/>
+        <v>1.46</v>
+      </c>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="6" t="inlineStr"/>
+      <c r="I27" s="6" t="n"/>
       <c r="J27" s="3" t="n">
-        <v>1362</v>
+        <v>39169</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>454</v>
+        <v>561</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
-      <c r="G28" s="4" t="inlineStr"/>
+        <v>1.98</v>
+      </c>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="n"/>
       <c r="J28" s="3" t="n">
-        <v>39169</v>
+        <v>68019</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>561</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
+        <v>1.77</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>6.72</v>
+      </c>
       <c r="H29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>0.7203820715741027</v>
+      </c>
       <c r="J29" s="3" t="n">
-        <v>68019</v>
+        <v>66907</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>2109</v>
+        <v>2633</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>copper</t>
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.47</v>
+        <v>2.24</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>6.72</v>
-      </c>
+        <v>3.56</v>
+      </c>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
       <c r="H30" s="5" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>0.7203820715741027</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I30" s="6" t="n"/>
       <c r="J30" s="3" t="n">
-        <v>66907</v>
+        <v>12437</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>2633</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>copper</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="3" t="n">
-        <v>12437</v>
-      </c>
-      <c r="K31" s="3" t="n">
         <v>386</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K31"/>
+  <autoFilter ref="A1:K30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Plot/exposures_meta_analysis_uterine_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_dietary.xlsx
@@ -640,7 +640,7 @@
         <v>62.8</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.2282168407301836</v>
+        <v>0.2282168407301835</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>3315</v>
@@ -739,7 +739,7 @@
         <v>24.9</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1753492059479154</v>
+        <v>0.1753492059479153</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>3315</v>
@@ -776,7 +776,7 @@
         <v>93.09999999999999</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.484788327891376</v>
+        <v>0.4847883278913757</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>90098</v>
@@ -974,7 +974,7 @@
         <v>46.3</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.3550326464827145</v>
+        <v>0.3550326464827144</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3331</v>
@@ -1011,7 +1011,7 @@
         <v>84.2</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.0290298668942214</v>
+        <v>0.02902986689422141</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>95991</v>
@@ -1048,7 +1048,7 @@
         <v>78.7</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8535116576994071</v>
+        <v>0.8535116576994072</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>4413</v>
@@ -1289,7 +1289,7 @@
         <v>73.59999999999999</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.7559650135603327</v>
+        <v>0.7559650135603323</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>411289</v>

--- a/Plot/exposures_meta_analysis_uterine_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_dietary.xlsx
@@ -553,17 +553,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>0.73</v>
@@ -575,29 +575,29 @@
       </c>
       <c r="I3" s="6" t="n"/>
       <c r="J3" s="3" t="n">
-        <v>74680</v>
+        <v>1082</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>412</v>
+        <v>541</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>legumes</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>0.49</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
@@ -606,84 +606,84 @@
       </c>
       <c r="I4" s="6" t="n"/>
       <c r="J4" s="3" t="n">
-        <v>843</v>
+        <v>74680</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>332</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>legumes</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>26.86</v>
-      </c>
+        <v>0.85</v>
+      </c>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
       <c r="H5" s="5" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>0.2282168407301835</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="n"/>
       <c r="J5" s="3" t="n">
-        <v>3315</v>
+        <v>843</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1227</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>mineral_supplements</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+        <v>0.71</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>26.86</v>
+      </c>
       <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="6" t="n"/>
+        <v>62.8</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.2282168407301835</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>3596</v>
+        <v>3315</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>709</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>vitamin_c</t>
+          <t>mineral_supplements</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -696,7 +696,7 @@
         <v>0.33</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
@@ -705,121 +705,121 @@
       </c>
       <c r="I7" s="6" t="n"/>
       <c r="J7" s="3" t="n">
-        <v>871</v>
+        <v>3596</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>232</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>beta-carotene</t>
+          <t>vitamin_c</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.46</v>
+        <v>0.33</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>5.64</v>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
       <c r="H8" s="5" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>0.1753492059479153</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I8" s="6" t="n"/>
       <c r="J8" s="3" t="n">
-        <v>3315</v>
+        <v>871</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>1227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>beta-carotene</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.37</v>
+        <v>0.46</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1.08</v>
+        <v>0.78</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>509.19</v>
+        <v>5.64</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>93.09999999999999</v>
+        <v>24.9</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.4847883278913757</v>
+        <v>0.1753492059479153</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>90098</v>
+        <v>3315</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>3100</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>antioxidants</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
+        <v>1.08</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>509.19</v>
+      </c>
       <c r="H10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="6" t="n"/>
+        <v>93.09999999999999</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.4847883278913757</v>
+      </c>
       <c r="J10" s="3" t="n">
-        <v>812</v>
+        <v>90098</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>417</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>garlic</t>
+          <t>antioxidants</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -829,10 +829,10 @@
         <v>0.65</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
@@ -841,109 +841,109 @@
       </c>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="3" t="n">
-        <v>1362</v>
+        <v>812</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>454</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>calcium</t>
+          <t>garlic</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1.09</v>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
       <c r="H12" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>0.084037740305833</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I12" s="6" t="n"/>
       <c r="J12" s="3" t="n">
-        <v>6240</v>
+        <v>1362</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1445</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>quercetin</t>
+          <t>calcium</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.68</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.44</v>
+        <v>0.55</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+        <v>0.84</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1.09</v>
+      </c>
       <c r="H13" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.084037740305833</v>
+      </c>
       <c r="J13" s="3" t="n">
-        <v>822</v>
+        <v>6240</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>424</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>quercetin</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.68</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="5" t="n">
-        <v>86.2</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="3" t="n">
-        <v>30376</v>
+        <v>822</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>2937</v>
+        <v>424</v>
       </c>
     </row>
     <row r="15">

--- a/Plot/exposures_meta_analysis_uterine_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_dietary.xlsx
@@ -529,13 +529,13 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
@@ -560,13 +560,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
@@ -591,13 +591,13 @@
         <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.73</v>
+        <v>0.71</v>
       </c>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
@@ -622,13 +622,13 @@
         <v>1</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0.49</v>
+        <v>0.47</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
@@ -653,25 +653,25 @@
         <v>3</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.71</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0.01</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>26.86</v>
+        <v>32.17</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.2282168407301835</v>
+        <v>0.2506814459510834</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>3315</v>
@@ -690,13 +690,13 @@
         <v>1</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.53</v>
+        <v>0.51</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
@@ -752,25 +752,25 @@
         <v>3</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.78</v>
+        <v>0.76</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.64</v>
+        <v>6.39</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>24.9</v>
+        <v>25.7</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>0.1753492059479153</v>
+        <v>0.1836147138174006</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>3315</v>
@@ -789,25 +789,25 @@
         <v>3</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.63</v>
+        <v>0.61</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>509.19</v>
+        <v>853.0599999999999</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>93.09999999999999</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.4847883278913757</v>
+        <v>0.4931648603872096</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>90098</v>
@@ -826,10 +826,10 @@
         <v>1</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>0.98</v>
@@ -857,13 +857,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.65</v>
+        <v>0.63</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
@@ -888,25 +888,25 @@
         <v>4</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.43</v>
+        <v>0.39</v>
       </c>
       <c r="G13" s="4" t="n">
         <v>1.09</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.084037740305833</v>
+        <v>0.09410146376052672</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>6240</v>
@@ -925,10 +925,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.68</v>
+        <v>0.66</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>1.01</v>
@@ -956,25 +956,25 @@
         <v>3</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.51</v>
+        <v>0.48</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>16.43</v>
+        <v>21.88</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>46.3</v>
+        <v>47.7</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.3550326464827144</v>
+        <v>0.3625177001442668</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3331</v>
@@ -996,7 +996,7 @@
         <v>0.73</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>1.13</v>
@@ -1005,13 +1005,13 @@
         <v>0</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>127.74</v>
+        <v>147.01</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>84.2</v>
+        <v>84.5</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.02902986689422141</v>
+        <v>0.0282125522798201</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>95991</v>
@@ -1030,25 +1030,25 @@
         <v>4</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="E17" s="4" t="n">
         <v>1.21</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.72</v>
+        <v>6.33</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>78.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8535116576994072</v>
+        <v>0.8911172970547432</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>4413</v>
@@ -1067,13 +1067,13 @@
         <v>1</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
@@ -1098,18 +1098,18 @@
         <v>2</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="5" t="n">
-        <v>59.9</v>
+        <v>60</v>
       </c>
       <c r="I19" s="6" t="n"/>
       <c r="J19" s="3" t="n">
@@ -1129,10 +1129,10 @@
         <v>1</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.74</v>
+        <v>0.72</v>
       </c>
       <c r="E20" s="4" t="n">
         <v>0.93</v>
@@ -1160,25 +1160,25 @@
         <v>5</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.6898302519232826</v>
+        <v>0.6742434715505108</v>
       </c>
       <c r="J21" s="3" t="n">
         <v>457863</v>
@@ -1200,22 +1200,22 @@
         <v>0.87</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>1689.46</v>
+        <v>2410.29</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>89.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.4263170110816271</v>
+        <v>0.2543666266957765</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>110943</v>
@@ -1234,25 +1234,25 @@
         <v>4</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>60.8</v>
+        <v>60.6</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.8631142054417384</v>
+        <v>0.8733935157460906</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>150854</v>
@@ -1280,16 +1280,16 @@
         <v>1.08</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>73.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.7559650135603323</v>
+        <v>0.7583025598842165</v>
       </c>
       <c r="J24" s="3" t="n">
         <v>411289</v>
@@ -1339,13 +1339,13 @@
         <v>1</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
@@ -1370,13 +1370,13 @@
         <v>2</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="F27" s="4" t="n"/>
       <c r="G27" s="4" t="n"/>
@@ -1432,25 +1432,25 @@
         <v>3</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.72</v>
+        <v>17.76</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>21.1</v>
+        <v>42.7</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.7203820715741027</v>
+        <v>0.5749186758153059</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>66907</v>
@@ -1469,13 +1469,13 @@
         <v>1</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.24</v>
+        <v>2.61</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.56</v>
+        <v>5.03</v>
       </c>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>

--- a/Plot/exposures_meta_analysis_uterine_dietary.xlsx
+++ b/Plot/exposures_meta_analysis_uterine_dietary.xlsx
@@ -807,7 +807,7 @@
         <v>93.40000000000001</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.4931648603872096</v>
+        <v>0.4931648603872101</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>90098</v>
@@ -906,7 +906,7 @@
         <v>1.2</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.09410146376052672</v>
+        <v>0.09410146376052661</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>6240</v>
@@ -974,7 +974,7 @@
         <v>47.7</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>0.3625177001442668</v>
+        <v>0.3625177001442669</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>3331</v>
@@ -1048,7 +1048,7 @@
         <v>77.40000000000001</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.8911172970547432</v>
+        <v>0.8911172970547433</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>4413</v>
@@ -1450,7 +1450,7 @@
         <v>42.7</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.5749186758153059</v>
+        <v>0.5749186758153051</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>66907</v>
